--- a/Grids Germany/No leap years/Bavaria insights/[Bavaria][Euclidean][Raw]Yearly_U_test.xlsx
+++ b/Grids Germany/No leap years/Bavaria insights/[Bavaria][Euclidean][Raw]Yearly_U_test.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,62 +429,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>YEAR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>mean_P1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>sd_P1</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>n_P1</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>mean_P2</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>sd_P2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>n_P2</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>U_statistic</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>p_Bonferroni</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Significant</t>
         </is>
@@ -488,13 +500,13 @@
         <v>1996</v>
       </c>
       <c r="C2" t="n">
-        <v>9.218733003709525</v>
+        <v>9.374943075828508</v>
       </c>
       <c r="D2" t="n">
-        <v>4.346974974916814</v>
+        <v>4.501974641505239</v>
       </c>
       <c r="E2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F2" t="n">
         <v>9.741887076998424</v>
@@ -506,10 +518,10 @@
         <v>19</v>
       </c>
       <c r="I2" t="n">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7836883650361984</v>
+        <v>0.9352416292303105</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
@@ -528,13 +540,13 @@
         <v>1997</v>
       </c>
       <c r="C3" t="n">
-        <v>5.352192479400731</v>
+        <v>5.603083118932457</v>
       </c>
       <c r="D3" t="n">
-        <v>2.997524969713206</v>
+        <v>3.190115671751316</v>
       </c>
       <c r="E3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F3" t="n">
         <v>13.75360584305639</v>
@@ -546,13 +558,13 @@
         <v>19</v>
       </c>
       <c r="I3" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J3" t="n">
-        <v>1.830278638930048e-07</v>
+        <v>5.427933156198331e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>5.490835916790143e-06</v>
+        <v>1.628379946859499e-05</v>
       </c>
       <c r="L3" t="b">
         <v>1</v>
@@ -568,13 +580,13 @@
         <v>1998</v>
       </c>
       <c r="C4" t="n">
-        <v>8.099575702125872</v>
+        <v>7.967728669566029</v>
       </c>
       <c r="D4" t="n">
-        <v>3.699080784961054</v>
+        <v>3.590937948702353</v>
       </c>
       <c r="E4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F4" t="n">
         <v>12.4044280724512</v>
@@ -586,13 +598,13 @@
         <v>19</v>
       </c>
       <c r="I4" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001033972710566995</v>
+        <v>0.0005824376923117234</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03101918131700984</v>
+        <v>0.0174731307693517</v>
       </c>
       <c r="L4" t="b">
         <v>1</v>
@@ -608,13 +620,13 @@
         <v>1999</v>
       </c>
       <c r="C5" t="n">
-        <v>7.517642546145202</v>
+        <v>7.487617133856258</v>
       </c>
       <c r="D5" t="n">
-        <v>3.373638224619604</v>
+        <v>3.326983036887407</v>
       </c>
       <c r="E5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F5" t="n">
         <v>16.6373287112017</v>
@@ -629,10 +641,10 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>5.00601038421188e-08</v>
+        <v>7.057183580218095e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>1.501803115263564e-06</v>
+        <v>2.117155074065429e-06</v>
       </c>
       <c r="L5" t="b">
         <v>1</v>
@@ -648,13 +660,13 @@
         <v>2000</v>
       </c>
       <c r="C6" t="n">
-        <v>10.40748702491613</v>
+        <v>10.7514496601196</v>
       </c>
       <c r="D6" t="n">
-        <v>3.864703556395863</v>
+        <v>3.938263626993844</v>
       </c>
       <c r="E6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F6" t="n">
         <v>13.20073540468435</v>
@@ -666,13 +678,13 @@
         <v>19</v>
       </c>
       <c r="I6" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008601304616119299</v>
+        <v>0.02132744514079924</v>
       </c>
       <c r="K6" t="n">
-        <v>0.258039138483579</v>
+        <v>0.6398233542239773</v>
       </c>
       <c r="L6" t="b">
         <v>0</v>
@@ -688,13 +700,13 @@
         <v>2001</v>
       </c>
       <c r="C7" t="n">
-        <v>5.63482760350766</v>
+        <v>5.348846481524114</v>
       </c>
       <c r="D7" t="n">
-        <v>3.932596735864329</v>
+        <v>3.474214152810247</v>
       </c>
       <c r="E7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F7" t="n">
         <v>10.36227136728289</v>
@@ -706,13 +718,13 @@
         <v>19</v>
       </c>
       <c r="I7" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="J7" t="n">
-        <v>7.467752166289718e-05</v>
+        <v>3.415281363208687e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002240325649886916</v>
+        <v>0.001024584408962606</v>
       </c>
       <c r="L7" t="b">
         <v>1</v>
@@ -728,13 +740,13 @@
         <v>2002</v>
       </c>
       <c r="C8" t="n">
-        <v>7.737237592497266</v>
+        <v>7.890701593038583</v>
       </c>
       <c r="D8" t="n">
-        <v>2.425882695265953</v>
+        <v>2.291108842369844</v>
       </c>
       <c r="E8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F8" t="n">
         <v>13.49648033602194</v>
@@ -746,13 +758,13 @@
         <v>19</v>
       </c>
       <c r="I8" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J8" t="n">
-        <v>5.538754927891404e-07</v>
+        <v>5.427933156198331e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>1.661626478367421e-05</v>
+        <v>1.628379946859499e-05</v>
       </c>
       <c r="L8" t="b">
         <v>1</v>
@@ -768,13 +780,13 @@
         <v>2003</v>
       </c>
       <c r="C9" t="n">
-        <v>9.155791200829317</v>
+        <v>9.620335539155608</v>
       </c>
       <c r="D9" t="n">
-        <v>4.74005892048272</v>
+        <v>4.256113875153188</v>
       </c>
       <c r="E9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F9" t="n">
         <v>13.85444618884498</v>
@@ -786,13 +798,13 @@
         <v>19</v>
       </c>
       <c r="I9" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0004825316312145503</v>
+        <v>0.0007104983619273451</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01447594893643651</v>
+        <v>0.02131495085782036</v>
       </c>
       <c r="L9" t="b">
         <v>1</v>
@@ -808,13 +820,13 @@
         <v>2004</v>
       </c>
       <c r="C10" t="n">
-        <v>9.090036481044528</v>
+        <v>9.289028010429481</v>
       </c>
       <c r="D10" t="n">
-        <v>3.665605080248729</v>
+        <v>3.309018993127022</v>
       </c>
       <c r="E10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F10" t="n">
         <v>14.79768811714228</v>
@@ -826,13 +838,13 @@
         <v>19</v>
       </c>
       <c r="I10" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J10" t="n">
-        <v>1.191275247692701e-05</v>
+        <v>1.146070609867433e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0003573825743078103</v>
+        <v>0.00034382118296023</v>
       </c>
       <c r="L10" t="b">
         <v>1</v>
@@ -848,13 +860,13 @@
         <v>2005</v>
       </c>
       <c r="C11" t="n">
-        <v>8.65759152464023</v>
+        <v>8.512110156646512</v>
       </c>
       <c r="D11" t="n">
-        <v>3.204027818213318</v>
+        <v>2.90339213969776</v>
       </c>
       <c r="E11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F11" t="n">
         <v>14.65912316225454</v>
@@ -866,13 +878,13 @@
         <v>19</v>
       </c>
       <c r="I11" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="J11" t="n">
-        <v>5.361051033399823e-05</v>
+        <v>6.112456655667056e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>0.001608315310019947</v>
+        <v>0.001833736996700117</v>
       </c>
       <c r="L11" t="b">
         <v>1</v>
@@ -888,13 +900,13 @@
         <v>2006</v>
       </c>
       <c r="C12" t="n">
-        <v>8.512437150373152</v>
+        <v>8.780948528635994</v>
       </c>
       <c r="D12" t="n">
-        <v>3.453725979199071</v>
+        <v>3.436357286015749</v>
       </c>
       <c r="E12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F12" t="n">
         <v>16.58186434591262</v>
@@ -909,10 +921,10 @@
         <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>6.708507279434098e-08</v>
+        <v>9.526002607574446e-08</v>
       </c>
       <c r="K12" t="n">
-        <v>2.012552183830229e-06</v>
+        <v>2.857800782272334e-06</v>
       </c>
       <c r="L12" t="b">
         <v>1</v>
@@ -928,13 +940,13 @@
         <v>2007</v>
       </c>
       <c r="C13" t="n">
-        <v>12.32881579427448</v>
+        <v>12.79773775428826</v>
       </c>
       <c r="D13" t="n">
-        <v>2.899077252501851</v>
+        <v>2.804629483074481</v>
       </c>
       <c r="E13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F13" t="n">
         <v>11.25710030093638</v>
@@ -946,10 +958,10 @@
         <v>19</v>
       </c>
       <c r="I13" t="n">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1467766899799145</v>
+        <v>0.04802699871964889</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -968,13 +980,13 @@
         <v>2008</v>
       </c>
       <c r="C14" t="n">
-        <v>7.890099487968016</v>
+        <v>8.294224605191687</v>
       </c>
       <c r="D14" t="n">
-        <v>2.16517764666012</v>
+        <v>2.177941339171464</v>
       </c>
       <c r="E14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F14" t="n">
         <v>12.48714214247377</v>
@@ -986,13 +998,13 @@
         <v>19</v>
       </c>
       <c r="I14" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J14" t="n">
-        <v>0.02215904454739236</v>
+        <v>0.03702708305422064</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6647713364217708</v>
+        <v>1</v>
       </c>
       <c r="L14" t="b">
         <v>0</v>
@@ -1008,13 +1020,13 @@
         <v>2009</v>
       </c>
       <c r="C15" t="n">
-        <v>11.45123128091713</v>
+        <v>11.57336354828818</v>
       </c>
       <c r="D15" t="n">
-        <v>2.443950467383471</v>
+        <v>2.410350913239512</v>
       </c>
       <c r="E15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F15" t="n">
         <v>14.22655552421116</v>
@@ -1026,13 +1038,13 @@
         <v>19</v>
       </c>
       <c r="I15" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0003245809905337601</v>
+        <v>0.000476141421532243</v>
       </c>
       <c r="K15" t="n">
-        <v>0.009737429716012803</v>
+        <v>0.01428424264596729</v>
       </c>
       <c r="L15" t="b">
         <v>1</v>
@@ -1048,13 +1060,13 @@
         <v>2010</v>
       </c>
       <c r="C16" t="n">
-        <v>8.79609981079266</v>
+        <v>8.579469962137727</v>
       </c>
       <c r="D16" t="n">
-        <v>3.329916379347231</v>
+        <v>3.104924611454454</v>
       </c>
       <c r="E16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F16" t="n">
         <v>11.91697181912828</v>
@@ -1066,13 +1078,13 @@
         <v>19</v>
       </c>
       <c r="I16" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0005860668055800342</v>
+        <v>0.0002842443918960535</v>
       </c>
       <c r="K16" t="n">
-        <v>0.01758200416740103</v>
+        <v>0.008527331756881607</v>
       </c>
       <c r="L16" t="b">
         <v>1</v>
@@ -1088,13 +1100,13 @@
         <v>2011</v>
       </c>
       <c r="C17" t="n">
-        <v>10.46642849263551</v>
+        <v>10.29702135534001</v>
       </c>
       <c r="D17" t="n">
-        <v>3.315329572347011</v>
+        <v>3.330542926245263</v>
       </c>
       <c r="E17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F17" t="n">
         <v>15.0967265982038</v>
@@ -1106,13 +1118,13 @@
         <v>19</v>
       </c>
       <c r="I17" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0005319567266736574</v>
+        <v>0.0003881690483723223</v>
       </c>
       <c r="K17" t="n">
-        <v>0.01595870180020972</v>
+        <v>0.01164507145116967</v>
       </c>
       <c r="L17" t="b">
         <v>1</v>
@@ -1128,13 +1140,13 @@
         <v>2012</v>
       </c>
       <c r="C18" t="n">
-        <v>8.129119707154432</v>
+        <v>8.644428325553235</v>
       </c>
       <c r="D18" t="n">
-        <v>4.589626065629774</v>
+        <v>4.669374103292974</v>
       </c>
       <c r="E18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F18" t="n">
         <v>13.81840868546317</v>
@@ -1146,13 +1158,13 @@
         <v>19</v>
       </c>
       <c r="I18" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0001581827247087803</v>
+        <v>0.0003501162650486686</v>
       </c>
       <c r="K18" t="n">
-        <v>0.004745481741263408</v>
+        <v>0.01050348795146006</v>
       </c>
       <c r="L18" t="b">
         <v>1</v>
@@ -1168,13 +1180,13 @@
         <v>2013</v>
       </c>
       <c r="C19" t="n">
-        <v>10.54107364090234</v>
+        <v>10.77122660330317</v>
       </c>
       <c r="D19" t="n">
-        <v>3.407499082890225</v>
+        <v>3.129912562078038</v>
       </c>
       <c r="E19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F19" t="n">
         <v>13.27526876549324</v>
@@ -1186,13 +1198,13 @@
         <v>19</v>
       </c>
       <c r="I19" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="J19" t="n">
-        <v>0.02068007225528007</v>
+        <v>0.02457815969375158</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6204021676584019</v>
+        <v>0.7373447908125472</v>
       </c>
       <c r="L19" t="b">
         <v>0</v>
@@ -1208,13 +1220,13 @@
         <v>2014</v>
       </c>
       <c r="C20" t="n">
-        <v>9.398879290959293</v>
+        <v>9.233259613631597</v>
       </c>
       <c r="D20" t="n">
-        <v>3.146256064133214</v>
+        <v>3.152381653909954</v>
       </c>
       <c r="E20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F20" t="n">
         <v>15.23673779294176</v>
@@ -1226,13 +1238,13 @@
         <v>19</v>
       </c>
       <c r="I20" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J20" t="n">
-        <v>4.833995322523418e-07</v>
+        <v>5.427933156198331e-07</v>
       </c>
       <c r="K20" t="n">
-        <v>1.450198596757025e-05</v>
+        <v>1.628379946859499e-05</v>
       </c>
       <c r="L20" t="b">
         <v>1</v>
@@ -1248,13 +1260,13 @@
         <v>2015</v>
       </c>
       <c r="C21" t="n">
-        <v>9.952445227148415</v>
+        <v>10.07233215682704</v>
       </c>
       <c r="D21" t="n">
-        <v>2.658754303058799</v>
+        <v>2.610744311598357</v>
       </c>
       <c r="E21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F21" t="n">
         <v>12.95074006456399</v>
@@ -1269,10 +1281,10 @@
         <v>81</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0008579010720209487</v>
+        <v>0.001393916027072069</v>
       </c>
       <c r="K21" t="n">
-        <v>0.02573703216062846</v>
+        <v>0.04181748081216207</v>
       </c>
       <c r="L21" t="b">
         <v>1</v>
@@ -1288,13 +1300,13 @@
         <v>2016</v>
       </c>
       <c r="C22" t="n">
-        <v>7.174394959236724</v>
+        <v>6.883949577172667</v>
       </c>
       <c r="D22" t="n">
-        <v>2.600046111619285</v>
+        <v>2.7115216701819</v>
       </c>
       <c r="E22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F22" t="n">
         <v>16.82260216909675</v>
@@ -1309,10 +1321,10 @@
         <v>2</v>
       </c>
       <c r="J22" t="n">
-        <v>6.708507279434098e-08</v>
+        <v>9.526002607574446e-08</v>
       </c>
       <c r="K22" t="n">
-        <v>2.012552183830229e-06</v>
+        <v>2.857800782272334e-06</v>
       </c>
       <c r="L22" t="b">
         <v>1</v>
@@ -1328,13 +1340,13 @@
         <v>2017</v>
       </c>
       <c r="C23" t="n">
-        <v>6.523026318870106</v>
+        <v>6.126140777943347</v>
       </c>
       <c r="D23" t="n">
-        <v>3.298729124143258</v>
+        <v>3.300169259355153</v>
       </c>
       <c r="E23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F23" t="n">
         <v>11.31369781029549</v>
@@ -1346,13 +1358,13 @@
         <v>19</v>
       </c>
       <c r="I23" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J23" t="n">
-        <v>2.418086306316322e-05</v>
+        <v>1.875102388929462e-05</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0007254258918948967</v>
+        <v>0.0005625307166788387</v>
       </c>
       <c r="L23" t="b">
         <v>1</v>
@@ -1368,13 +1380,13 @@
         <v>2018</v>
       </c>
       <c r="C24" t="n">
-        <v>13.56557506181914</v>
+        <v>13.71086492192515</v>
       </c>
       <c r="D24" t="n">
-        <v>2.327984832659965</v>
+        <v>2.328117140683982</v>
       </c>
       <c r="E24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F24" t="n">
         <v>16.91059775304148</v>
@@ -1389,10 +1401,10 @@
         <v>52</v>
       </c>
       <c r="J24" t="n">
-        <v>4.284243898160414e-05</v>
+        <v>6.852701193915714e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>0.001285273169448124</v>
+        <v>0.002055810358174714</v>
       </c>
       <c r="L24" t="b">
         <v>1</v>
@@ -1408,13 +1420,13 @@
         <v>2019</v>
       </c>
       <c r="C25" t="n">
-        <v>9.769906897227825</v>
+        <v>9.662897996118518</v>
       </c>
       <c r="D25" t="n">
-        <v>3.789359398683418</v>
+        <v>3.955844347185335</v>
       </c>
       <c r="E25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F25" t="n">
         <v>13.05196073666137</v>
@@ -1426,13 +1438,13 @@
         <v>19</v>
       </c>
       <c r="I25" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="J25" t="n">
-        <v>0.006811132003560291</v>
+        <v>0.00794899579919988</v>
       </c>
       <c r="K25" t="n">
-        <v>0.2043339601068087</v>
+        <v>0.2384698739759964</v>
       </c>
       <c r="L25" t="b">
         <v>0</v>
@@ -1448,13 +1460,13 @@
         <v>2020</v>
       </c>
       <c r="C26" t="n">
-        <v>11.24152545798649</v>
+        <v>11.28649454618397</v>
       </c>
       <c r="D26" t="n">
-        <v>2.486195874691789</v>
+        <v>2.53857747709072</v>
       </c>
       <c r="E26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F26" t="n">
         <v>16.11670766051256</v>
@@ -1469,10 +1481,10 @@
         <v>13</v>
       </c>
       <c r="J26" t="n">
-        <v>3.200844853880141e-07</v>
+        <v>4.713621458961539e-07</v>
       </c>
       <c r="K26" t="n">
-        <v>9.602534561640423e-06</v>
+        <v>1.414086437688462e-05</v>
       </c>
       <c r="L26" t="b">
         <v>1</v>
@@ -1488,13 +1500,13 @@
         <v>2021</v>
       </c>
       <c r="C27" t="n">
-        <v>5.919055940550047</v>
+        <v>6.277142478100932</v>
       </c>
       <c r="D27" t="n">
-        <v>3.220827724154385</v>
+        <v>3.242082362857533</v>
       </c>
       <c r="E27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F27" t="n">
         <v>15.34409778379662</v>
@@ -1506,13 +1518,13 @@
         <v>19</v>
       </c>
       <c r="I27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J27" t="n">
-        <v>1.035535340437375e-07</v>
+        <v>1.991584925480624e-07</v>
       </c>
       <c r="K27" t="n">
-        <v>3.106606021312125e-06</v>
+        <v>5.974754776441873e-06</v>
       </c>
       <c r="L27" t="b">
         <v>1</v>
@@ -1528,13 +1540,13 @@
         <v>2022</v>
       </c>
       <c r="C28" t="n">
-        <v>8.028796784092524</v>
+        <v>8.082598695277985</v>
       </c>
       <c r="D28" t="n">
-        <v>2.735053369720392</v>
+        <v>2.756323550644204</v>
       </c>
       <c r="E28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F28" t="n">
         <v>13.81051435890068</v>
@@ -1549,10 +1561,10 @@
         <v>56</v>
       </c>
       <c r="J28" t="n">
-        <v>6.691028588979331e-05</v>
+        <v>0.0001075007295492875</v>
       </c>
       <c r="K28" t="n">
-        <v>0.002007308576693799</v>
+        <v>0.003225021886478626</v>
       </c>
       <c r="L28" t="b">
         <v>1</v>
@@ -1568,13 +1580,13 @@
         <v>2023</v>
       </c>
       <c r="C29" t="n">
-        <v>7.704502006194553</v>
+        <v>7.799138537871109</v>
       </c>
       <c r="D29" t="n">
-        <v>2.561073886985252</v>
+        <v>2.434706520861246</v>
       </c>
       <c r="E29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F29" t="n">
         <v>17.90506427011922</v>
@@ -1589,10 +1601,10 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>5.00601038421188e-08</v>
+        <v>7.057183580218095e-08</v>
       </c>
       <c r="K29" t="n">
-        <v>1.501803115263564e-06</v>
+        <v>2.117155074065429e-06</v>
       </c>
       <c r="L29" t="b">
         <v>1</v>
@@ -1608,13 +1620,13 @@
         <v>2024</v>
       </c>
       <c r="C30" t="n">
-        <v>8.479860608261056</v>
+        <v>7.811086540898112</v>
       </c>
       <c r="D30" t="n">
-        <v>5.376832159360492</v>
+        <v>4.709142060259341</v>
       </c>
       <c r="E30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F30" t="n">
         <v>14.71382292018908</v>
@@ -1626,13 +1638,13 @@
         <v>19</v>
       </c>
       <c r="I30" t="n">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0007806983846482445</v>
+        <v>0.0001857946653424578</v>
       </c>
       <c r="K30" t="n">
-        <v>0.02342095153944734</v>
+        <v>0.005573839960273733</v>
       </c>
       <c r="L30" t="b">
         <v>1</v>
@@ -1648,13 +1660,13 @@
         <v>2025</v>
       </c>
       <c r="C31" t="n">
-        <v>11.02137899042717</v>
+        <v>11.17437898819239</v>
       </c>
       <c r="D31" t="n">
-        <v>2.841869252249932</v>
+        <v>2.462344793434265</v>
       </c>
       <c r="E31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F31" t="n">
         <v>15.15510629768969</v>
@@ -1666,13 +1678,13 @@
         <v>19</v>
       </c>
       <c r="I31" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="J31" t="n">
-        <v>3.045679503082353e-05</v>
+        <v>1.46801018407284e-05</v>
       </c>
       <c r="K31" t="n">
-        <v>0.000913703850924706</v>
+        <v>0.000440403055221852</v>
       </c>
       <c r="L31" t="b">
         <v>1</v>
@@ -1688,13 +1700,13 @@
         <v>1996</v>
       </c>
       <c r="C32" t="n">
-        <v>67.19496539677969</v>
+        <v>66.36245833021778</v>
       </c>
       <c r="D32" t="n">
-        <v>12.90378197681371</v>
+        <v>12.56483462555514</v>
       </c>
       <c r="E32" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F32" t="n">
         <v>82.44650632307057</v>
@@ -1706,13 +1718,13 @@
         <v>19</v>
       </c>
       <c r="I32" t="n">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="J32" t="n">
-        <v>0.0004374167278753596</v>
+        <v>0.0001495863719521272</v>
       </c>
       <c r="K32" t="n">
-        <v>0.01312250183626079</v>
+        <v>0.004487591158563817</v>
       </c>
       <c r="L32" t="b">
         <v>1</v>
@@ -1728,13 +1740,13 @@
         <v>1997</v>
       </c>
       <c r="C33" t="n">
-        <v>68.54755323600597</v>
+        <v>68.79930262149253</v>
       </c>
       <c r="D33" t="n">
-        <v>11.09328576178991</v>
+        <v>10.34704172659703</v>
       </c>
       <c r="E33" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F33" t="n">
         <v>75.51898639952185</v>
@@ -1746,13 +1758,13 @@
         <v>19</v>
       </c>
       <c r="I33" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J33" t="n">
-        <v>0.01163816627608508</v>
+        <v>0.01371506541438565</v>
       </c>
       <c r="K33" t="n">
-        <v>0.3491449882825525</v>
+        <v>0.4114519624315695</v>
       </c>
       <c r="L33" t="b">
         <v>0</v>
@@ -1768,13 +1780,13 @@
         <v>1998</v>
       </c>
       <c r="C34" t="n">
-        <v>72.00911795245386</v>
+        <v>73.21737584924927</v>
       </c>
       <c r="D34" t="n">
-        <v>8.093344186654827</v>
+        <v>8.843157988660607</v>
       </c>
       <c r="E34" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F34" t="n">
         <v>84.65587356077718</v>
@@ -1786,13 +1798,13 @@
         <v>19</v>
       </c>
       <c r="I34" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="J34" t="n">
-        <v>3.826142756040716e-05</v>
+        <v>0.0003155750685131454</v>
       </c>
       <c r="K34" t="n">
-        <v>0.001147842826812215</v>
+        <v>0.009467252055394362</v>
       </c>
       <c r="L34" t="b">
         <v>1</v>
@@ -1808,13 +1820,13 @@
         <v>1999</v>
       </c>
       <c r="C35" t="n">
-        <v>78.06838204449679</v>
+        <v>77.96718293916972</v>
       </c>
       <c r="D35" t="n">
-        <v>7.54517970071266</v>
+        <v>7.46419504450221</v>
       </c>
       <c r="E35" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F35" t="n">
         <v>74.08859959747519</v>
@@ -1826,10 +1838,10 @@
         <v>19</v>
       </c>
       <c r="I35" t="n">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="J35" t="n">
-        <v>0.0821052825711137</v>
+        <v>0.08795413503199695</v>
       </c>
       <c r="K35" t="n">
         <v>1</v>
@@ -1848,13 +1860,13 @@
         <v>2000</v>
       </c>
       <c r="C36" t="n">
-        <v>73.18102952897507</v>
+        <v>72.5763284029296</v>
       </c>
       <c r="D36" t="n">
-        <v>9.373981577168935</v>
+        <v>9.613396108218753</v>
       </c>
       <c r="E36" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F36" t="n">
         <v>82.86890588464344</v>
@@ -1866,13 +1878,13 @@
         <v>19</v>
       </c>
       <c r="I36" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J36" t="n">
-        <v>0.001242990038883185</v>
+        <v>0.001048570109538549</v>
       </c>
       <c r="K36" t="n">
-        <v>0.03728970116649555</v>
+        <v>0.03145710328615646</v>
       </c>
       <c r="L36" t="b">
         <v>1</v>
@@ -1888,13 +1900,13 @@
         <v>2001</v>
       </c>
       <c r="C37" t="n">
-        <v>77.63145568936483</v>
+        <v>78.45003252796386</v>
       </c>
       <c r="D37" t="n">
-        <v>8.967387249407539</v>
+        <v>8.014127894365251</v>
       </c>
       <c r="E37" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F37" t="n">
         <v>84.34126930959718</v>
@@ -1906,13 +1918,13 @@
         <v>19</v>
       </c>
       <c r="I37" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J37" t="n">
-        <v>0.01348711356572764</v>
+        <v>0.01984736066582055</v>
       </c>
       <c r="K37" t="n">
-        <v>0.4046134069718292</v>
+        <v>0.5954208199746166</v>
       </c>
       <c r="L37" t="b">
         <v>0</v>
@@ -1928,13 +1940,13 @@
         <v>2002</v>
       </c>
       <c r="C38" t="n">
-        <v>74.94346438771903</v>
+        <v>75.4107811822404</v>
       </c>
       <c r="D38" t="n">
-        <v>9.48928042141169</v>
+        <v>9.530365710236309</v>
       </c>
       <c r="E38" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F38" t="n">
         <v>78.61165339333274</v>
@@ -1949,7 +1961,7 @@
         <v>164</v>
       </c>
       <c r="J38" t="n">
-        <v>0.2446577021026661</v>
+        <v>0.3431606204893868</v>
       </c>
       <c r="K38" t="n">
         <v>1</v>
@@ -1968,13 +1980,13 @@
         <v>2003</v>
       </c>
       <c r="C39" t="n">
-        <v>62.58008709219162</v>
+        <v>61.88441156597038</v>
       </c>
       <c r="D39" t="n">
-        <v>9.180645044695241</v>
+        <v>9.190476921264345</v>
       </c>
       <c r="E39" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F39" t="n">
         <v>71.78648154039018</v>
@@ -1986,16 +1998,16 @@
         <v>19</v>
       </c>
       <c r="I39" t="n">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J39" t="n">
-        <v>0.002126574788868804</v>
+        <v>0.001268591601623397</v>
       </c>
       <c r="K39" t="n">
-        <v>0.06379724366606412</v>
+        <v>0.0380577480487019</v>
       </c>
       <c r="L39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2008,13 +2020,13 @@
         <v>2004</v>
       </c>
       <c r="C40" t="n">
-        <v>69.20113463989499</v>
+        <v>68.84672230914956</v>
       </c>
       <c r="D40" t="n">
-        <v>7.968100037994323</v>
+        <v>7.084372603326319</v>
       </c>
       <c r="E40" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F40" t="n">
         <v>72.17191811551128</v>
@@ -2026,10 +2038,10 @@
         <v>19</v>
       </c>
       <c r="I40" t="n">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="J40" t="n">
-        <v>0.1618961583856021</v>
+        <v>0.1100532269450499</v>
       </c>
       <c r="K40" t="n">
         <v>1</v>
@@ -2048,13 +2060,13 @@
         <v>2005</v>
       </c>
       <c r="C41" t="n">
-        <v>76.35711900965923</v>
+        <v>75.74541951267827</v>
       </c>
       <c r="D41" t="n">
-        <v>11.0028048099831</v>
+        <v>10.98957937399442</v>
       </c>
       <c r="E41" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F41" t="n">
         <v>78.07140416223898</v>
@@ -2066,10 +2078,10 @@
         <v>19</v>
       </c>
       <c r="I41" t="n">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="J41" t="n">
-        <v>0.8650586834684142</v>
+        <v>0.7045575343964623</v>
       </c>
       <c r="K41" t="n">
         <v>1</v>
@@ -2088,13 +2100,13 @@
         <v>2006</v>
       </c>
       <c r="C42" t="n">
-        <v>76.57735873918917</v>
+        <v>78.376256589893</v>
       </c>
       <c r="D42" t="n">
-        <v>9.35373607866735</v>
+        <v>9.014123540747134</v>
       </c>
       <c r="E42" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F42" t="n">
         <v>74.76855804556091</v>
@@ -2106,10 +2118,10 @@
         <v>19</v>
       </c>
       <c r="I42" t="n">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="J42" t="n">
-        <v>0.5218238301757392</v>
+        <v>0.1671922015505145</v>
       </c>
       <c r="K42" t="n">
         <v>1</v>
@@ -2128,13 +2140,13 @@
         <v>2007</v>
       </c>
       <c r="C43" t="n">
-        <v>58.30974374314899</v>
+        <v>57.95797005826576</v>
       </c>
       <c r="D43" t="n">
-        <v>7.247986480741459</v>
+        <v>6.832054892369209</v>
       </c>
       <c r="E43" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F43" t="n">
         <v>82.3422043885454</v>
@@ -2149,10 +2161,10 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>5.00601038421188e-08</v>
+        <v>7.057183580218095e-08</v>
       </c>
       <c r="K43" t="n">
-        <v>1.501803115263564e-06</v>
+        <v>2.117155074065429e-06</v>
       </c>
       <c r="L43" t="b">
         <v>1</v>
@@ -2168,13 +2180,13 @@
         <v>2008</v>
       </c>
       <c r="C44" t="n">
-        <v>76.97487454964549</v>
+        <v>76.86374673603166</v>
       </c>
       <c r="D44" t="n">
-        <v>6.173197497500278</v>
+        <v>6.528167549034745</v>
       </c>
       <c r="E44" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F44" t="n">
         <v>79.41839085932429</v>
@@ -2186,10 +2198,10 @@
         <v>19</v>
       </c>
       <c r="I44" t="n">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="J44" t="n">
-        <v>0.2665103114753677</v>
+        <v>0.2786492808876931</v>
       </c>
       <c r="K44" t="n">
         <v>1</v>
@@ -2208,13 +2220,13 @@
         <v>2009</v>
       </c>
       <c r="C45" t="n">
-        <v>65.7134579348123</v>
+        <v>65.01488874825159</v>
       </c>
       <c r="D45" t="n">
-        <v>12.2569729839803</v>
+        <v>11.70735027190615</v>
       </c>
       <c r="E45" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F45" t="n">
         <v>80.73499420763783</v>
@@ -2226,13 +2238,13 @@
         <v>19</v>
       </c>
       <c r="I45" t="n">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="J45" t="n">
-        <v>0.0003962642764906895</v>
+        <v>0.0002301261921361123</v>
       </c>
       <c r="K45" t="n">
-        <v>0.01188792829472069</v>
+        <v>0.006903785764083369</v>
       </c>
       <c r="L45" t="b">
         <v>1</v>
@@ -2248,13 +2260,13 @@
         <v>2010</v>
       </c>
       <c r="C46" t="n">
-        <v>67.274723867329</v>
+        <v>67.41376965030184</v>
       </c>
       <c r="D46" t="n">
-        <v>10.41782940616315</v>
+        <v>10.62762802617774</v>
       </c>
       <c r="E46" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F46" t="n">
         <v>81.47364445947311</v>
@@ -2269,10 +2281,10 @@
         <v>66</v>
       </c>
       <c r="J46" t="n">
-        <v>0.0001948745382146378</v>
+        <v>0.0003155750685131454</v>
       </c>
       <c r="K46" t="n">
-        <v>0.005846236146439135</v>
+        <v>0.009467252055394362</v>
       </c>
       <c r="L46" t="b">
         <v>1</v>
@@ -2288,13 +2300,13 @@
         <v>2011</v>
       </c>
       <c r="C47" t="n">
-        <v>62.45833354442663</v>
+        <v>63.1040669393044</v>
       </c>
       <c r="D47" t="n">
-        <v>8.992880599224225</v>
+        <v>9.655778665043313</v>
       </c>
       <c r="E47" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F47" t="n">
         <v>81.27680660448448</v>
@@ -2306,13 +2318,13 @@
         <v>19</v>
       </c>
       <c r="I47" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J47" t="n">
-        <v>1.606677569768074e-06</v>
+        <v>6.096284739821612e-06</v>
       </c>
       <c r="K47" t="n">
-        <v>4.820032709304223e-05</v>
+        <v>0.0001828885421946484</v>
       </c>
       <c r="L47" t="b">
         <v>1</v>
@@ -2328,13 +2340,13 @@
         <v>2012</v>
       </c>
       <c r="C48" t="n">
-        <v>70.46489655643043</v>
+        <v>70.08742491703077</v>
       </c>
       <c r="D48" t="n">
-        <v>10.5874707783174</v>
+        <v>11.81502069836564</v>
       </c>
       <c r="E48" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F48" t="n">
         <v>77.5343884882554</v>
@@ -2349,7 +2361,7 @@
         <v>133</v>
       </c>
       <c r="J48" t="n">
-        <v>0.04839330007790107</v>
+        <v>0.07384997829416654</v>
       </c>
       <c r="K48" t="n">
         <v>1</v>
@@ -2368,13 +2380,13 @@
         <v>2013</v>
       </c>
       <c r="C49" t="n">
-        <v>74.66142071725126</v>
+        <v>74.9189486837808</v>
       </c>
       <c r="D49" t="n">
-        <v>8.019264443011959</v>
+        <v>8.247894000864045</v>
       </c>
       <c r="E49" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F49" t="n">
         <v>84.02985287489028</v>
@@ -2386,13 +2398,13 @@
         <v>19</v>
       </c>
       <c r="I49" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="J49" t="n">
-        <v>0.0005860668055800342</v>
+        <v>0.001393916027072069</v>
       </c>
       <c r="K49" t="n">
-        <v>0.01758200416740103</v>
+        <v>0.04181748081216207</v>
       </c>
       <c r="L49" t="b">
         <v>1</v>
@@ -2408,13 +2420,13 @@
         <v>2014</v>
       </c>
       <c r="C50" t="n">
-        <v>75.33923219425698</v>
+        <v>76.05964791461024</v>
       </c>
       <c r="D50" t="n">
-        <v>7.659610882030707</v>
+        <v>8.494835337472725</v>
       </c>
       <c r="E50" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F50" t="n">
         <v>86.94240279088098</v>
@@ -2426,13 +2438,13 @@
         <v>19</v>
       </c>
       <c r="I50" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="J50" t="n">
-        <v>5.062305784764319e-06</v>
+        <v>4.853023332476458e-05</v>
       </c>
       <c r="K50" t="n">
-        <v>0.0001518691735429296</v>
+        <v>0.001455906999742938</v>
       </c>
       <c r="L50" t="b">
         <v>1</v>
@@ -2448,13 +2460,13 @@
         <v>2015</v>
       </c>
       <c r="C51" t="n">
-        <v>64.96951139814615</v>
+        <v>65.35388486128048</v>
       </c>
       <c r="D51" t="n">
-        <v>7.222125139349548</v>
+        <v>8.303597407867873</v>
       </c>
       <c r="E51" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F51" t="n">
         <v>78.25433328190194</v>
@@ -2466,13 +2478,13 @@
         <v>19</v>
       </c>
       <c r="I51" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J51" t="n">
-        <v>1.236004823829212e-06</v>
+        <v>1.146070609867433e-05</v>
       </c>
       <c r="K51" t="n">
-        <v>3.708014471487635e-05</v>
+        <v>0.00034382118296023</v>
       </c>
       <c r="L51" t="b">
         <v>1</v>
@@ -2488,13 +2500,13 @@
         <v>2016</v>
       </c>
       <c r="C52" t="n">
-        <v>75.54383403907356</v>
+        <v>76.43206519358354</v>
       </c>
       <c r="D52" t="n">
-        <v>8.673529485745783</v>
+        <v>7.670023275945284</v>
       </c>
       <c r="E52" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F52" t="n">
         <v>77.59858028649062</v>
@@ -2506,10 +2518,10 @@
         <v>19</v>
       </c>
       <c r="I52" t="n">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="J52" t="n">
-        <v>0.9895702107225923</v>
+        <v>0.8709091430964933</v>
       </c>
       <c r="K52" t="n">
         <v>1</v>
@@ -2528,13 +2540,13 @@
         <v>2017</v>
       </c>
       <c r="C53" t="n">
-        <v>72.68186050808771</v>
+        <v>73.75317011000202</v>
       </c>
       <c r="D53" t="n">
-        <v>9.560835902956217</v>
+        <v>9.98674402761992</v>
       </c>
       <c r="E53" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F53" t="n">
         <v>83.93709892156937</v>
@@ -2546,16 +2558,16 @@
         <v>19</v>
       </c>
       <c r="I53" t="n">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J53" t="n">
-        <v>0.0005860668055800342</v>
+        <v>0.002644304406362379</v>
       </c>
       <c r="K53" t="n">
-        <v>0.01758200416740103</v>
+        <v>0.07932913219087137</v>
       </c>
       <c r="L53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -2568,13 +2580,13 @@
         <v>2018</v>
       </c>
       <c r="C54" t="n">
-        <v>65.41243155399512</v>
+        <v>65.68636823315506</v>
       </c>
       <c r="D54" t="n">
-        <v>7.216140497312944</v>
+        <v>7.227425787218049</v>
       </c>
       <c r="E54" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F54" t="n">
         <v>75.34012312255827</v>
@@ -2586,13 +2598,13 @@
         <v>19</v>
       </c>
       <c r="I54" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J54" t="n">
-        <v>0.000293475164563048</v>
+        <v>0.0003881690483723223</v>
       </c>
       <c r="K54" t="n">
-        <v>0.00880425493689144</v>
+        <v>0.01164507145116967</v>
       </c>
       <c r="L54" t="b">
         <v>1</v>
@@ -2608,13 +2620,13 @@
         <v>2019</v>
       </c>
       <c r="C55" t="n">
-        <v>62.29603352331981</v>
+        <v>61.43508589521757</v>
       </c>
       <c r="D55" t="n">
-        <v>14.42050708406591</v>
+        <v>14.20525202584966</v>
       </c>
       <c r="E55" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F55" t="n">
         <v>75.51484690917351</v>
@@ -2626,13 +2638,13 @@
         <v>19</v>
       </c>
       <c r="I55" t="n">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="J55" t="n">
-        <v>0.008601304616119299</v>
+        <v>0.004093045844708801</v>
       </c>
       <c r="K55" t="n">
-        <v>0.258039138483579</v>
+        <v>0.122791375341264</v>
       </c>
       <c r="L55" t="b">
         <v>0</v>
@@ -2648,13 +2660,13 @@
         <v>2020</v>
       </c>
       <c r="C56" t="n">
-        <v>56.3191596707487</v>
+        <v>56.41912042673148</v>
       </c>
       <c r="D56" t="n">
-        <v>10.64537109351958</v>
+        <v>10.1461672345322</v>
       </c>
       <c r="E56" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F56" t="n">
         <v>74.13290653049076</v>
@@ -2666,13 +2678,13 @@
         <v>19</v>
       </c>
       <c r="I56" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>1.056264409035028e-05</v>
+        <v>3.18611527792797e-06</v>
       </c>
       <c r="K56" t="n">
-        <v>0.0003168793227105084</v>
+        <v>9.558345833783911e-05</v>
       </c>
       <c r="L56" t="b">
         <v>1</v>
@@ -2688,13 +2700,13 @@
         <v>2021</v>
       </c>
       <c r="C57" t="n">
-        <v>68.65521751775491</v>
+        <v>67.58153898042367</v>
       </c>
       <c r="D57" t="n">
-        <v>10.70552343768349</v>
+        <v>11.10396385439757</v>
       </c>
       <c r="E57" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F57" t="n">
         <v>78.9478935628005</v>
@@ -2706,13 +2718,13 @@
         <v>19</v>
       </c>
       <c r="I57" t="n">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="J57" t="n">
-        <v>0.002757722098661697</v>
+        <v>0.002017988592121406</v>
       </c>
       <c r="K57" t="n">
-        <v>0.0827316629598509</v>
+        <v>0.06053965776364217</v>
       </c>
       <c r="L57" t="b">
         <v>0</v>
@@ -2728,13 +2740,13 @@
         <v>2022</v>
       </c>
       <c r="C58" t="n">
-        <v>69.91585107114867</v>
+        <v>69.14785319428704</v>
       </c>
       <c r="D58" t="n">
-        <v>9.070815300299424</v>
+        <v>9.046922986830531</v>
       </c>
       <c r="E58" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F58" t="n">
         <v>81.60031893801097</v>
@@ -2746,13 +2758,13 @@
         <v>19</v>
       </c>
       <c r="I58" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="J58" t="n">
-        <v>0.0001581827247087803</v>
+        <v>9.615654461282442e-05</v>
       </c>
       <c r="K58" t="n">
-        <v>0.004745481741263408</v>
+        <v>0.002884696338384733</v>
       </c>
       <c r="L58" t="b">
         <v>1</v>
@@ -2768,13 +2780,13 @@
         <v>2023</v>
       </c>
       <c r="C59" t="n">
-        <v>78.54264460335952</v>
+        <v>79.15469196117556</v>
       </c>
       <c r="D59" t="n">
-        <v>7.739530192331803</v>
+        <v>7.750710068598494</v>
       </c>
       <c r="E59" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F59" t="n">
         <v>75.01862621253576</v>
@@ -2786,13 +2798,13 @@
         <v>19</v>
       </c>
       <c r="I59" t="n">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J59" t="n">
-        <v>0.05465489064878856</v>
+        <v>0.02635874162747212</v>
       </c>
       <c r="K59" t="n">
-        <v>1</v>
+        <v>0.7907622488241637</v>
       </c>
       <c r="L59" t="b">
         <v>0</v>
@@ -2808,13 +2820,13 @@
         <v>2024</v>
       </c>
       <c r="C60" t="n">
-        <v>72.83006559223485</v>
+        <v>73.9077428843503</v>
       </c>
       <c r="D60" t="n">
-        <v>10.35368814660176</v>
+        <v>9.362001434155278</v>
       </c>
       <c r="E60" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F60" t="n">
         <v>78.7272623685774</v>
@@ -2829,7 +2841,7 @@
         <v>144</v>
       </c>
       <c r="J60" t="n">
-        <v>0.09173600418801962</v>
+        <v>0.1363246840317136</v>
       </c>
       <c r="K60" t="n">
         <v>1</v>
@@ -2848,13 +2860,13 @@
         <v>2025</v>
       </c>
       <c r="C61" t="n">
-        <v>68.46468544720354</v>
+        <v>69.23714764080307</v>
       </c>
       <c r="D61" t="n">
-        <v>8.991472901905942</v>
+        <v>8.627883737543851</v>
       </c>
       <c r="E61" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F61" t="n">
         <v>79.0813988885908</v>
@@ -2869,10 +2881,10 @@
         <v>74</v>
       </c>
       <c r="J61" t="n">
-        <v>0.0004374167278753596</v>
+        <v>0.0007104983619273451</v>
       </c>
       <c r="K61" t="n">
-        <v>0.01312250183626079</v>
+        <v>0.02131495085782036</v>
       </c>
       <c r="L61" t="b">
         <v>1</v>
@@ -2888,13 +2900,13 @@
         <v>1996</v>
       </c>
       <c r="C62" t="n">
-        <v>88.81972117628696</v>
+        <v>87.11764750934367</v>
       </c>
       <c r="D62" t="n">
-        <v>19.42447418770532</v>
+        <v>19.37171254507899</v>
       </c>
       <c r="E62" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F62" t="n">
         <v>93.59513195785853</v>
@@ -2906,10 +2918,10 @@
         <v>19</v>
       </c>
       <c r="I62" t="n">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="J62" t="n">
-        <v>0.3533430443555126</v>
+        <v>0.1756731342850328</v>
       </c>
       <c r="K62" t="n">
         <v>1</v>
@@ -2928,13 +2940,13 @@
         <v>1997</v>
       </c>
       <c r="C63" t="n">
-        <v>103.4972173329394</v>
+        <v>102.7603578212116</v>
       </c>
       <c r="D63" t="n">
-        <v>12.32340276561054</v>
+        <v>11.88626513045974</v>
       </c>
       <c r="E63" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F63" t="n">
         <v>48.2514448611572</v>
@@ -2946,13 +2958,13 @@
         <v>19</v>
       </c>
       <c r="I63" t="n">
-        <v>418</v>
+        <v>399</v>
       </c>
       <c r="J63" t="n">
-        <v>5.00601038421188e-08</v>
+        <v>7.057183580218095e-08</v>
       </c>
       <c r="K63" t="n">
-        <v>1.501803115263564e-06</v>
+        <v>2.117155074065429e-06</v>
       </c>
       <c r="L63" t="b">
         <v>1</v>
@@ -2968,13 +2980,13 @@
         <v>1998</v>
       </c>
       <c r="C64" t="n">
-        <v>109.3513832569301</v>
+        <v>109.6699819980681</v>
       </c>
       <c r="D64" t="n">
-        <v>8.901058877605385</v>
+        <v>8.768889866885653</v>
       </c>
       <c r="E64" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F64" t="n">
         <v>123.3644123328353</v>
@@ -2986,13 +2998,13 @@
         <v>19</v>
       </c>
       <c r="I64" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J64" t="n">
-        <v>0.001134037511943275</v>
+        <v>0.001530570869210911</v>
       </c>
       <c r="K64" t="n">
-        <v>0.03402112535829825</v>
+        <v>0.04591712607632732</v>
       </c>
       <c r="L64" t="b">
         <v>1</v>
@@ -3008,13 +3020,13 @@
         <v>1999</v>
       </c>
       <c r="C65" t="n">
-        <v>121.8633472074455</v>
+        <v>122.0829684805723</v>
       </c>
       <c r="D65" t="n">
-        <v>10.85816569524396</v>
+        <v>9.804428444152792</v>
       </c>
       <c r="E65" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F65" t="n">
         <v>35.86713315747547</v>
@@ -3026,13 +3038,13 @@
         <v>19</v>
       </c>
       <c r="I65" t="n">
-        <v>418</v>
+        <v>399</v>
       </c>
       <c r="J65" t="n">
-        <v>5.00601038421188e-08</v>
+        <v>7.057183580218095e-08</v>
       </c>
       <c r="K65" t="n">
-        <v>1.501803115263564e-06</v>
+        <v>2.117155074065429e-06</v>
       </c>
       <c r="L65" t="b">
         <v>1</v>
@@ -3048,13 +3060,13 @@
         <v>2000</v>
       </c>
       <c r="C66" t="n">
-        <v>105.5661007012713</v>
+        <v>105.1516033973172</v>
       </c>
       <c r="D66" t="n">
-        <v>13.28577194440025</v>
+        <v>13.87382395621302</v>
       </c>
       <c r="E66" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F66" t="n">
         <v>99.91027405763941</v>
@@ -3066,10 +3078,10 @@
         <v>19</v>
       </c>
       <c r="I66" t="n">
-        <v>264</v>
+        <v>247</v>
       </c>
       <c r="J66" t="n">
-        <v>0.1541956400351703</v>
+        <v>0.2030370754756237</v>
       </c>
       <c r="K66" t="n">
         <v>1</v>
@@ -3088,13 +3100,13 @@
         <v>2001</v>
       </c>
       <c r="C67" t="n">
-        <v>125.7396508123941</v>
+        <v>126.3473824257962</v>
       </c>
       <c r="D67" t="n">
-        <v>8.600101647532522</v>
+        <v>7.581751275487875</v>
       </c>
       <c r="E67" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F67" t="n">
         <v>113.6848731372879</v>
@@ -3106,13 +3118,13 @@
         <v>19</v>
       </c>
       <c r="I67" t="n">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="J67" t="n">
-        <v>0.02903189505293685</v>
+        <v>0.02457815969375158</v>
       </c>
       <c r="K67" t="n">
-        <v>0.8709568515881057</v>
+        <v>0.7373447908125472</v>
       </c>
       <c r="L67" t="b">
         <v>0</v>
@@ -3128,13 +3140,13 @@
         <v>2002</v>
       </c>
       <c r="C68" t="n">
-        <v>95.02273416568704</v>
+        <v>96.54173231390442</v>
       </c>
       <c r="D68" t="n">
-        <v>20.3487176485856</v>
+        <v>20.53683280759769</v>
       </c>
       <c r="E68" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F68" t="n">
         <v>90.50870576815777</v>
@@ -3146,10 +3158,10 @@
         <v>19</v>
       </c>
       <c r="I68" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J68" t="n">
-        <v>0.4562028338837304</v>
+        <v>0.2908427576877802</v>
       </c>
       <c r="K68" t="n">
         <v>1</v>
@@ -3168,13 +3180,13 @@
         <v>2003</v>
       </c>
       <c r="C69" t="n">
-        <v>72.66925621480409</v>
+        <v>71.35122359157494</v>
       </c>
       <c r="D69" t="n">
-        <v>13.53429079673891</v>
+        <v>13.21662104854003</v>
       </c>
       <c r="E69" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F69" t="n">
         <v>53.65176677448166</v>
@@ -3186,13 +3198,13 @@
         <v>19</v>
       </c>
       <c r="I69" t="n">
-        <v>323</v>
+        <v>304</v>
       </c>
       <c r="J69" t="n">
-        <v>0.003003459393580646</v>
+        <v>0.004851493247946607</v>
       </c>
       <c r="K69" t="n">
-        <v>0.09010378180741938</v>
+        <v>0.1455447974383982</v>
       </c>
       <c r="L69" t="b">
         <v>0</v>
@@ -3208,13 +3220,13 @@
         <v>2004</v>
       </c>
       <c r="C70" t="n">
-        <v>101.6759334042586</v>
+        <v>100.8216871486047</v>
       </c>
       <c r="D70" t="n">
-        <v>15.31484638843703</v>
+        <v>13.14657412972867</v>
       </c>
       <c r="E70" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F70" t="n">
         <v>46.86548521601161</v>
@@ -3226,13 +3238,13 @@
         <v>19</v>
       </c>
       <c r="I70" t="n">
-        <v>418</v>
+        <v>399</v>
       </c>
       <c r="J70" t="n">
-        <v>5.00601038421188e-08</v>
+        <v>7.057183580218095e-08</v>
       </c>
       <c r="K70" t="n">
-        <v>1.501803115263564e-06</v>
+        <v>2.117155074065429e-06</v>
       </c>
       <c r="L70" t="b">
         <v>1</v>
@@ -3248,13 +3260,13 @@
         <v>2005</v>
       </c>
       <c r="C71" t="n">
-        <v>117.7950850410231</v>
+        <v>118.3776989038366</v>
       </c>
       <c r="D71" t="n">
-        <v>14.69097964005551</v>
+        <v>15.03516915747448</v>
       </c>
       <c r="E71" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F71" t="n">
         <v>80.94924483793871</v>
@@ -3266,13 +3278,13 @@
         <v>19</v>
       </c>
       <c r="I71" t="n">
-        <v>372</v>
+        <v>355</v>
       </c>
       <c r="J71" t="n">
-        <v>2.152481834216518e-05</v>
+        <v>2.692652717951664e-05</v>
       </c>
       <c r="K71" t="n">
-        <v>0.0006457445502649554</v>
+        <v>0.0008077958153854991</v>
       </c>
       <c r="L71" t="b">
         <v>1</v>
@@ -3288,13 +3300,13 @@
         <v>2006</v>
       </c>
       <c r="C72" t="n">
-        <v>120.177325016292</v>
+        <v>121.1674779206452</v>
       </c>
       <c r="D72" t="n">
-        <v>12.25936541742772</v>
+        <v>12.68531319147432</v>
       </c>
       <c r="E72" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F72" t="n">
         <v>66.26962470049884</v>
@@ -3306,13 +3318,13 @@
         <v>19</v>
       </c>
       <c r="I72" t="n">
-        <v>417</v>
+        <v>398</v>
       </c>
       <c r="J72" t="n">
-        <v>5.796996173396205e-08</v>
+        <v>8.202112267204054e-08</v>
       </c>
       <c r="K72" t="n">
-        <v>1.739098852018861e-06</v>
+        <v>2.460633680161216e-06</v>
       </c>
       <c r="L72" t="b">
         <v>1</v>
@@ -3328,13 +3340,13 @@
         <v>2007</v>
       </c>
       <c r="C73" t="n">
-        <v>49.10878497306869</v>
+        <v>47.54830243536662</v>
       </c>
       <c r="D73" t="n">
-        <v>18.45717733958123</v>
+        <v>16.67550733773868</v>
       </c>
       <c r="E73" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F73" t="n">
         <v>108.3481465596467</v>
@@ -3349,10 +3361,10 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>5.00601038421188e-08</v>
+        <v>7.057183580218095e-08</v>
       </c>
       <c r="K73" t="n">
-        <v>1.501803115263564e-06</v>
+        <v>2.117155074065429e-06</v>
       </c>
       <c r="L73" t="b">
         <v>1</v>
@@ -3368,13 +3380,13 @@
         <v>2008</v>
       </c>
       <c r="C74" t="n">
-        <v>124.9829303852811</v>
+        <v>124.8447412185873</v>
       </c>
       <c r="D74" t="n">
-        <v>5.761898338939472</v>
+        <v>5.765227482563352</v>
       </c>
       <c r="E74" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F74" t="n">
         <v>92.30446615435694</v>
@@ -3386,13 +3398,13 @@
         <v>19</v>
       </c>
       <c r="I74" t="n">
-        <v>417</v>
+        <v>398</v>
       </c>
       <c r="J74" t="n">
-        <v>5.796996173396205e-08</v>
+        <v>8.202112267204054e-08</v>
       </c>
       <c r="K74" t="n">
-        <v>1.739098852018861e-06</v>
+        <v>2.460633680161216e-06</v>
       </c>
       <c r="L74" t="b">
         <v>1</v>
@@ -3408,13 +3420,13 @@
         <v>2009</v>
       </c>
       <c r="C75" t="n">
-        <v>84.60370715920914</v>
+        <v>83.03349307494571</v>
       </c>
       <c r="D75" t="n">
-        <v>19.03957065960413</v>
+        <v>18.36506041416533</v>
       </c>
       <c r="E75" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F75" t="n">
         <v>65.85161706422782</v>
@@ -3426,13 +3438,13 @@
         <v>19</v>
       </c>
       <c r="I75" t="n">
-        <v>322</v>
+        <v>302</v>
       </c>
       <c r="J75" t="n">
-        <v>0.0032690189024479</v>
+        <v>0.005734923839296028</v>
       </c>
       <c r="K75" t="n">
-        <v>0.09807056707343699</v>
+        <v>0.1720477151788808</v>
       </c>
       <c r="L75" t="b">
         <v>0</v>
@@ -3448,13 +3460,13 @@
         <v>2010</v>
       </c>
       <c r="C76" t="n">
-        <v>85.50124762575807</v>
+        <v>85.14617203661058</v>
       </c>
       <c r="D76" t="n">
-        <v>17.75431682382477</v>
+        <v>18.54257639422645</v>
       </c>
       <c r="E76" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F76" t="n">
         <v>101.7479732279043</v>
@@ -3469,13 +3481,13 @@
         <v>83</v>
       </c>
       <c r="J76" t="n">
-        <v>0.001033972710566995</v>
+        <v>0.001679471238188246</v>
       </c>
       <c r="K76" t="n">
-        <v>0.03101918131700984</v>
+        <v>0.05038413714564739</v>
       </c>
       <c r="L76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -3488,13 +3500,13 @@
         <v>2011</v>
       </c>
       <c r="C77" t="n">
-        <v>66.27987687363181</v>
+        <v>65.53193723540511</v>
       </c>
       <c r="D77" t="n">
-        <v>14.27146907512028</v>
+        <v>13.9723844232881</v>
       </c>
       <c r="E77" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F77" t="n">
         <v>97.21802746864689</v>
@@ -3506,13 +3518,13 @@
         <v>19</v>
       </c>
       <c r="I77" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J77" t="n">
-        <v>7.257091171772516e-07</v>
+        <v>8.253251407017387e-07</v>
       </c>
       <c r="K77" t="n">
-        <v>2.177127351531755e-05</v>
+        <v>2.475975422105216e-05</v>
       </c>
       <c r="L77" t="b">
         <v>1</v>
@@ -3528,13 +3540,13 @@
         <v>2012</v>
       </c>
       <c r="C78" t="n">
-        <v>102.7123448039611</v>
+        <v>103.5208110497427</v>
       </c>
       <c r="D78" t="n">
-        <v>13.36446826522918</v>
+        <v>12.26607659617808</v>
       </c>
       <c r="E78" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F78" t="n">
         <v>73.01195674607136</v>
@@ -3546,13 +3558,13 @@
         <v>19</v>
       </c>
       <c r="I78" t="n">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="J78" t="n">
-        <v>3.94085181440346e-06</v>
+        <v>2.445640551201002e-06</v>
       </c>
       <c r="K78" t="n">
-        <v>0.0001182255544321038</v>
+        <v>7.336921653603004e-05</v>
       </c>
       <c r="L78" t="b">
         <v>1</v>
@@ -3568,13 +3580,13 @@
         <v>2013</v>
       </c>
       <c r="C79" t="n">
-        <v>108.5871160830159</v>
+        <v>109.0202145351734</v>
       </c>
       <c r="D79" t="n">
-        <v>12.58425895390151</v>
+        <v>12.72643305433843</v>
       </c>
       <c r="E79" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F79" t="n">
         <v>95.60340367108536</v>
@@ -3586,10 +3598,10 @@
         <v>19</v>
       </c>
       <c r="I79" t="n">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="J79" t="n">
-        <v>0.7438158570028419</v>
+        <v>0.786514361486491</v>
       </c>
       <c r="K79" t="n">
         <v>1</v>
@@ -3608,13 +3620,13 @@
         <v>2014</v>
       </c>
       <c r="C80" t="n">
-        <v>84.99590941118788</v>
+        <v>85.7154500774636</v>
       </c>
       <c r="D80" t="n">
-        <v>12.76358270616511</v>
+        <v>13.00981539945299</v>
       </c>
       <c r="E80" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F80" t="n">
         <v>111.6125045549966</v>
@@ -3626,13 +3638,13 @@
         <v>19</v>
       </c>
       <c r="I80" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J80" t="n">
-        <v>8.287791050984357e-06</v>
+        <v>1.659700346225223e-05</v>
       </c>
       <c r="K80" t="n">
-        <v>0.0002486337315295307</v>
+        <v>0.000497910103867567</v>
       </c>
       <c r="L80" t="b">
         <v>1</v>
@@ -3648,13 +3660,13 @@
         <v>2015</v>
       </c>
       <c r="C81" t="n">
-        <v>84.07586579755019</v>
+        <v>83.20068185597859</v>
       </c>
       <c r="D81" t="n">
-        <v>13.1251475577873</v>
+        <v>12.889718292391</v>
       </c>
       <c r="E81" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F81" t="n">
         <v>51.41768249816989</v>
@@ -3666,13 +3678,13 @@
         <v>19</v>
       </c>
       <c r="I81" t="n">
-        <v>418</v>
+        <v>399</v>
       </c>
       <c r="J81" t="n">
-        <v>5.00601038421188e-08</v>
+        <v>7.057183580218095e-08</v>
       </c>
       <c r="K81" t="n">
-        <v>1.501803115263564e-06</v>
+        <v>2.117155074065429e-06</v>
       </c>
       <c r="L81" t="b">
         <v>1</v>
@@ -3688,13 +3700,13 @@
         <v>2016</v>
       </c>
       <c r="C82" t="n">
-        <v>114.700359896062</v>
+        <v>115.9448035834634</v>
       </c>
       <c r="D82" t="n">
-        <v>11.80661213787805</v>
+        <v>11.73773187454392</v>
       </c>
       <c r="E82" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F82" t="n">
         <v>55.39790050919205</v>
@@ -3706,13 +3718,13 @@
         <v>19</v>
       </c>
       <c r="I82" t="n">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="J82" t="n">
-        <v>0.0003587519020525188</v>
+        <v>0.0002558466624784525</v>
       </c>
       <c r="K82" t="n">
-        <v>0.01076255706157556</v>
+        <v>0.007675399874353576</v>
       </c>
       <c r="L82" t="b">
         <v>1</v>
@@ -3728,13 +3740,13 @@
         <v>2017</v>
       </c>
       <c r="C83" t="n">
-        <v>99.13480666291581</v>
+        <v>100.7954239498627</v>
       </c>
       <c r="D83" t="n">
-        <v>22.42946526400302</v>
+        <v>23.16849307009401</v>
       </c>
       <c r="E83" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F83" t="n">
         <v>104.9580768561005</v>
@@ -3746,10 +3758,10 @@
         <v>19</v>
       </c>
       <c r="I83" t="n">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="J83" t="n">
-        <v>0.5218238301757392</v>
+        <v>0.8709091430964933</v>
       </c>
       <c r="K83" t="n">
         <v>1</v>
@@ -3768,13 +3780,13 @@
         <v>2018</v>
       </c>
       <c r="C84" t="n">
-        <v>75.68417397274006</v>
+        <v>75.12865545703605</v>
       </c>
       <c r="D84" t="n">
-        <v>15.41774785391294</v>
+        <v>15.26718161459544</v>
       </c>
       <c r="E84" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F84" t="n">
         <v>64.60223170664848</v>
@@ -3786,13 +3798,13 @@
         <v>19</v>
       </c>
       <c r="I84" t="n">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="J84" t="n">
-        <v>0.01797835517549631</v>
+        <v>0.02635874162747212</v>
       </c>
       <c r="K84" t="n">
-        <v>0.5393506552648895</v>
+        <v>0.7907622488241637</v>
       </c>
       <c r="L84" t="b">
         <v>0</v>
@@ -3808,13 +3820,13 @@
         <v>2019</v>
       </c>
       <c r="C85" t="n">
-        <v>65.22405914577418</v>
+        <v>63.37594327786864</v>
       </c>
       <c r="D85" t="n">
-        <v>20.8660477879858</v>
+        <v>19.51497198447264</v>
       </c>
       <c r="E85" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F85" t="n">
         <v>52.24526086830332</v>
@@ -3826,10 +3838,10 @@
         <v>19</v>
       </c>
       <c r="I85" t="n">
-        <v>287</v>
+        <v>268</v>
       </c>
       <c r="J85" t="n">
-        <v>0.04274561821833003</v>
+        <v>0.06551763448058548</v>
       </c>
       <c r="K85" t="n">
         <v>1</v>
@@ -3848,13 +3860,13 @@
         <v>2020</v>
       </c>
       <c r="C86" t="n">
-        <v>45.94588699166156</v>
+        <v>43.55552837273621</v>
       </c>
       <c r="D86" t="n">
-        <v>14.26647758510058</v>
+        <v>10.73094646630122</v>
       </c>
       <c r="E86" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F86" t="n">
         <v>58.05476049584161</v>
@@ -3866,10 +3878,10 @@
         <v>19</v>
       </c>
       <c r="I86" t="n">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="J86" t="n">
-        <v>0.09173600418801962</v>
+        <v>0.04222483612320902</v>
       </c>
       <c r="K86" t="n">
         <v>1</v>
@@ -3888,13 +3900,13 @@
         <v>2021</v>
       </c>
       <c r="C87" t="n">
-        <v>88.28608520255547</v>
+        <v>87.01794605839385</v>
       </c>
       <c r="D87" t="n">
-        <v>11.11923387893065</v>
+        <v>12.58299754806997</v>
       </c>
       <c r="E87" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F87" t="n">
         <v>66.47600105127712</v>
@@ -3906,13 +3918,13 @@
         <v>19</v>
       </c>
       <c r="I87" t="n">
-        <v>371</v>
+        <v>344</v>
       </c>
       <c r="J87" t="n">
-        <v>2.418086306316322e-05</v>
+        <v>9.615654461282442e-05</v>
       </c>
       <c r="K87" t="n">
-        <v>0.0007254258918948967</v>
+        <v>0.002884696338384733</v>
       </c>
       <c r="L87" t="b">
         <v>1</v>
@@ -3928,13 +3940,13 @@
         <v>2022</v>
       </c>
       <c r="C88" t="n">
-        <v>100.7269339278451</v>
+        <v>98.84004364811892</v>
       </c>
       <c r="D88" t="n">
-        <v>20.46752601498556</v>
+        <v>18.77709323419446</v>
       </c>
       <c r="E88" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F88" t="n">
         <v>99.20477057326816</v>
@@ -3946,10 +3958,10 @@
         <v>19</v>
       </c>
       <c r="I88" t="n">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="J88" t="n">
-        <v>0.8856632032926034</v>
+        <v>0.6845519562136833</v>
       </c>
       <c r="K88" t="n">
         <v>1</v>
@@ -3968,13 +3980,13 @@
         <v>2023</v>
       </c>
       <c r="C89" t="n">
-        <v>122.0315861884572</v>
+        <v>123.2641783445804</v>
       </c>
       <c r="D89" t="n">
-        <v>9.456537500095175</v>
+        <v>9.554162163040287</v>
       </c>
       <c r="E89" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F89" t="n">
         <v>65.0107790576557</v>
@@ -3986,13 +3998,13 @@
         <v>19</v>
       </c>
       <c r="I89" t="n">
-        <v>417</v>
+        <v>398</v>
       </c>
       <c r="J89" t="n">
-        <v>5.796996173396205e-08</v>
+        <v>8.202112267204054e-08</v>
       </c>
       <c r="K89" t="n">
-        <v>1.739098852018861e-06</v>
+        <v>2.460633680161216e-06</v>
       </c>
       <c r="L89" t="b">
         <v>1</v>
@@ -4008,13 +4020,13 @@
         <v>2024</v>
       </c>
       <c r="C90" t="n">
-        <v>108.1828840840855</v>
+        <v>109.8822048573118</v>
       </c>
       <c r="D90" t="n">
-        <v>20.93218670035007</v>
+        <v>20.19339666957323</v>
       </c>
       <c r="E90" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F90" t="n">
         <v>88.30874164379733</v>
@@ -4026,10 +4038,10 @@
         <v>19</v>
       </c>
       <c r="I90" t="n">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="J90" t="n">
-        <v>0.0733112816583633</v>
+        <v>0.04802699871964889</v>
       </c>
       <c r="K90" t="n">
         <v>1</v>
@@ -4048,13 +4060,13 @@
         <v>2025</v>
       </c>
       <c r="C91" t="n">
-        <v>71.10863882839163</v>
+        <v>71.85466139154627</v>
       </c>
       <c r="D91" t="n">
-        <v>15.94127700219539</v>
+        <v>16.47043149069308</v>
       </c>
       <c r="E91" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F91" t="n">
         <v>90.5370269655818</v>
@@ -4066,13 +4078,13 @@
         <v>19</v>
       </c>
       <c r="I91" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J91" t="n">
-        <v>0.000293475164563048</v>
+        <v>0.0005824376923117234</v>
       </c>
       <c r="K91" t="n">
-        <v>0.00880425493689144</v>
+        <v>0.0174731307693517</v>
       </c>
       <c r="L91" t="b">
         <v>1</v>
@@ -4088,13 +4100,13 @@
         <v>1996</v>
       </c>
       <c r="C92" t="n">
-        <v>11.32208734670922</v>
+        <v>11.51814400296181</v>
       </c>
       <c r="D92" t="n">
-        <v>3.785368701767826</v>
+        <v>3.893110377184475</v>
       </c>
       <c r="E92" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F92" t="n">
         <v>12.04665769611015</v>
@@ -4106,10 +4118,10 @@
         <v>19</v>
       </c>
       <c r="I92" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J92" t="n">
-        <v>0.7241268885030063</v>
+        <v>0.9352416292303105</v>
       </c>
       <c r="K92" t="n">
         <v>1</v>
@@ -4128,13 +4140,13 @@
         <v>1997</v>
       </c>
       <c r="C93" t="n">
-        <v>8.062871328631626</v>
+        <v>8.224514851057027</v>
       </c>
       <c r="D93" t="n">
-        <v>2.050332681195978</v>
+        <v>2.181927112673629</v>
       </c>
       <c r="E93" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F93" t="n">
         <v>17.34472832953499</v>
@@ -4149,10 +4161,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>5.00601038421188e-08</v>
+        <v>7.057183580218095e-08</v>
       </c>
       <c r="K93" t="n">
-        <v>1.501803115263564e-06</v>
+        <v>2.117155074065429e-06</v>
       </c>
       <c r="L93" t="b">
         <v>1</v>
@@ -4168,13 +4180,13 @@
         <v>1998</v>
       </c>
       <c r="C94" t="n">
-        <v>10.28428424761775</v>
+        <v>10.23903871462889</v>
       </c>
       <c r="D94" t="n">
-        <v>3.327990895871074</v>
+        <v>3.211874586649687</v>
       </c>
       <c r="E94" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F94" t="n">
         <v>14.30827623439731</v>
@@ -4186,13 +4198,13 @@
         <v>19</v>
       </c>
       <c r="I94" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="J94" t="n">
-        <v>0.0008579010720209487</v>
+        <v>0.0009523299145770314</v>
       </c>
       <c r="K94" t="n">
-        <v>0.02573703216062846</v>
+        <v>0.02856989743731094</v>
       </c>
       <c r="L94" t="b">
         <v>1</v>
@@ -4208,13 +4220,13 @@
         <v>1999</v>
       </c>
       <c r="C95" t="n">
-        <v>9.782660926270793</v>
+        <v>9.821797854832276</v>
       </c>
       <c r="D95" t="n">
-        <v>3.241218190204259</v>
+        <v>3.226089501667601</v>
       </c>
       <c r="E95" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F95" t="n">
         <v>19.18830716340246</v>
@@ -4229,10 +4241,10 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>5.00601038421188e-08</v>
+        <v>7.057183580218095e-08</v>
       </c>
       <c r="K95" t="n">
-        <v>1.501803115263564e-06</v>
+        <v>2.117155074065429e-06</v>
       </c>
       <c r="L95" t="b">
         <v>1</v>
@@ -4248,13 +4260,13 @@
         <v>2000</v>
       </c>
       <c r="C96" t="n">
-        <v>12.59021093117197</v>
+        <v>12.75987877019029</v>
       </c>
       <c r="D96" t="n">
-        <v>3.56577890190418</v>
+        <v>3.49683827804519</v>
       </c>
       <c r="E96" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F96" t="n">
         <v>15.83782217091444</v>
@@ -4266,13 +4278,13 @@
         <v>19</v>
       </c>
       <c r="I96" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J96" t="n">
-        <v>0.004199072509118142</v>
+        <v>0.006228927993530219</v>
       </c>
       <c r="K96" t="n">
-        <v>0.1259721752735443</v>
+        <v>0.1868678398059065</v>
       </c>
       <c r="L96" t="b">
         <v>0</v>
@@ -4288,13 +4300,13 @@
         <v>2001</v>
       </c>
       <c r="C97" t="n">
-        <v>7.710023035530937</v>
+        <v>7.431310179142296</v>
       </c>
       <c r="D97" t="n">
-        <v>3.503094746202597</v>
+        <v>3.089270364100749</v>
       </c>
       <c r="E97" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F97" t="n">
         <v>12.12603121574433</v>
@@ -4306,13 +4318,13 @@
         <v>19</v>
       </c>
       <c r="I97" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="J97" t="n">
-        <v>7.467752166289718e-05</v>
+        <v>3.415281363208687e-05</v>
       </c>
       <c r="K97" t="n">
-        <v>0.002240325649886916</v>
+        <v>0.001024584408962606</v>
       </c>
       <c r="L97" t="b">
         <v>1</v>
@@ -4328,13 +4340,13 @@
         <v>2002</v>
       </c>
       <c r="C98" t="n">
-        <v>9.937364572746331</v>
+        <v>9.949574101248212</v>
       </c>
       <c r="D98" t="n">
-        <v>2.047178609419535</v>
+        <v>1.944112159069459</v>
       </c>
       <c r="E98" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F98" t="n">
         <v>16.58598069289329</v>
@@ -4349,10 +4361,10 @@
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>5.00601038421188e-08</v>
+        <v>7.057183580218095e-08</v>
       </c>
       <c r="K98" t="n">
-        <v>1.501803115263564e-06</v>
+        <v>2.117155074065429e-06</v>
       </c>
       <c r="L98" t="b">
         <v>1</v>
@@ -4368,13 +4380,13 @@
         <v>2003</v>
       </c>
       <c r="C99" t="n">
-        <v>11.30477168254816</v>
+        <v>11.64988744490471</v>
       </c>
       <c r="D99" t="n">
-        <v>3.812232740904807</v>
+        <v>3.47975342707563</v>
       </c>
       <c r="E99" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F99" t="n">
         <v>16.20970067114892</v>
@@ -4389,10 +4401,10 @@
         <v>42</v>
       </c>
       <c r="J99" t="n">
-        <v>1.342662223774586e-05</v>
+        <v>2.116971972456703e-05</v>
       </c>
       <c r="K99" t="n">
-        <v>0.0004027986671323758</v>
+        <v>0.0006350915917370109</v>
       </c>
       <c r="L99" t="b">
         <v>1</v>
@@ -4408,13 +4420,13 @@
         <v>2004</v>
       </c>
       <c r="C100" t="n">
-        <v>11.56664278417794</v>
+        <v>11.75963460805692</v>
       </c>
       <c r="D100" t="n">
-        <v>3.560587024660212</v>
+        <v>3.321564572833797</v>
       </c>
       <c r="E100" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F100" t="n">
         <v>17.52015246461304</v>
@@ -4426,13 +4438,13 @@
         <v>19</v>
       </c>
       <c r="I100" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="J100" t="n">
-        <v>7.334055465928286e-06</v>
+        <v>6.096284739821612e-06</v>
       </c>
       <c r="K100" t="n">
-        <v>0.0002200216639778486</v>
+        <v>0.0001828885421946484</v>
       </c>
       <c r="L100" t="b">
         <v>1</v>
@@ -4448,13 +4460,13 @@
         <v>2005</v>
       </c>
       <c r="C101" t="n">
-        <v>10.92603937192705</v>
+        <v>10.81070063857784</v>
       </c>
       <c r="D101" t="n">
-        <v>2.726138338806166</v>
+        <v>2.403177589010687</v>
       </c>
       <c r="E101" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F101" t="n">
         <v>17.49601118880279</v>
@@ -4466,13 +4478,13 @@
         <v>19</v>
       </c>
       <c r="I101" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="J101" t="n">
-        <v>7.334055465928286e-06</v>
+        <v>6.92638467472005e-06</v>
       </c>
       <c r="K101" t="n">
-        <v>0.0002200216639778486</v>
+        <v>0.0002077915402416015</v>
       </c>
       <c r="L101" t="b">
         <v>1</v>
@@ -4488,13 +4500,13 @@
         <v>2006</v>
       </c>
       <c r="C102" t="n">
-        <v>10.37093698892331</v>
+        <v>10.55503315848781</v>
       </c>
       <c r="D102" t="n">
-        <v>3.768919065541252</v>
+        <v>3.838398556056051</v>
       </c>
       <c r="E102" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F102" t="n">
         <v>19.04890299851548</v>
@@ -4509,10 +4521,10 @@
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>5.00601038421188e-08</v>
+        <v>7.057183580218095e-08</v>
       </c>
       <c r="K102" t="n">
-        <v>1.501803115263564e-06</v>
+        <v>2.117155074065429e-06</v>
       </c>
       <c r="L102" t="b">
         <v>1</v>
@@ -4528,13 +4540,13 @@
         <v>2007</v>
       </c>
       <c r="C103" t="n">
-        <v>15.20284448823971</v>
+        <v>15.51651229188113</v>
       </c>
       <c r="D103" t="n">
-        <v>2.052818796092063</v>
+        <v>1.986578299154245</v>
       </c>
       <c r="E103" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F103" t="n">
         <v>13.45911352781813</v>
@@ -4549,10 +4561,10 @@
         <v>307</v>
       </c>
       <c r="J103" t="n">
-        <v>0.01080093620285118</v>
+        <v>0.003755694203448776</v>
       </c>
       <c r="K103" t="n">
-        <v>0.3240280860855353</v>
+        <v>0.1126708261034633</v>
       </c>
       <c r="L103" t="b">
         <v>0</v>
@@ -4568,13 +4580,13 @@
         <v>2008</v>
       </c>
       <c r="C104" t="n">
-        <v>9.906617749482768</v>
+        <v>10.2613434051902</v>
       </c>
       <c r="D104" t="n">
-        <v>2.143044665623753</v>
+        <v>2.226541101113953</v>
       </c>
       <c r="E104" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F104" t="n">
         <v>15.01937998620064</v>
@@ -4586,13 +4598,13 @@
         <v>19</v>
       </c>
       <c r="I104" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J104" t="n">
-        <v>0.0007806983846482445</v>
+        <v>0.001393916027072069</v>
       </c>
       <c r="K104" t="n">
-        <v>0.02342095153944734</v>
+        <v>0.04181748081216207</v>
       </c>
       <c r="L104" t="b">
         <v>1</v>
@@ -4608,13 +4620,13 @@
         <v>2009</v>
       </c>
       <c r="C105" t="n">
-        <v>13.85846723434327</v>
+        <v>14.03008977383583</v>
       </c>
       <c r="D105" t="n">
-        <v>1.880355931764731</v>
+        <v>1.807538439124153</v>
       </c>
       <c r="E105" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F105" t="n">
         <v>16.70303390989812</v>
@@ -4626,13 +4638,13 @@
         <v>19</v>
       </c>
       <c r="I105" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J105" t="n">
-        <v>1.702245028961376e-05</v>
+        <v>3.033581960970787e-05</v>
       </c>
       <c r="K105" t="n">
-        <v>0.0005106735086884128</v>
+        <v>0.0009100745882912359</v>
       </c>
       <c r="L105" t="b">
         <v>1</v>
@@ -4648,13 +4660,13 @@
         <v>2010</v>
       </c>
       <c r="C106" t="n">
-        <v>11.56268934019838</v>
+        <v>11.48073166216713</v>
       </c>
       <c r="D106" t="n">
-        <v>3.137421715658277</v>
+        <v>3.071189804179448</v>
       </c>
       <c r="E106" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F106" t="n">
         <v>14.62972671662694</v>
@@ -4666,13 +4678,13 @@
         <v>19</v>
       </c>
       <c r="I106" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J106" t="n">
-        <v>0.0007099870380201763</v>
+        <v>0.0008643278263233195</v>
       </c>
       <c r="K106" t="n">
-        <v>0.02129961114060529</v>
+        <v>0.02592983478969958</v>
       </c>
       <c r="L106" t="b">
         <v>1</v>
@@ -4688,13 +4700,13 @@
         <v>2011</v>
       </c>
       <c r="C107" t="n">
-        <v>13.38703013191899</v>
+        <v>13.29881648249784</v>
       </c>
       <c r="D107" t="n">
-        <v>2.994808659703443</v>
+        <v>3.039309875671053</v>
       </c>
       <c r="E107" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F107" t="n">
         <v>17.56223637167371</v>
@@ -4706,13 +4718,13 @@
         <v>19</v>
       </c>
       <c r="I107" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="J107" t="n">
-        <v>0.0002651788368361755</v>
+        <v>0.0002558466624784525</v>
       </c>
       <c r="K107" t="n">
-        <v>0.007955365105085266</v>
+        <v>0.007675399874353576</v>
       </c>
       <c r="L107" t="b">
         <v>1</v>
@@ -4728,13 +4740,13 @@
         <v>2012</v>
       </c>
       <c r="C108" t="n">
-        <v>9.895066127193255</v>
+        <v>10.18062370115742</v>
       </c>
       <c r="D108" t="n">
-        <v>3.825782762739588</v>
+        <v>3.683774303163956</v>
       </c>
       <c r="E108" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F108" t="n">
         <v>16.71507523917331</v>
@@ -4749,10 +4761,10 @@
         <v>40</v>
       </c>
       <c r="J108" t="n">
-        <v>1.056264409035028e-05</v>
+        <v>1.659700346225223e-05</v>
       </c>
       <c r="K108" t="n">
-        <v>0.0003168793227105084</v>
+        <v>0.000497910103867567</v>
       </c>
       <c r="L108" t="b">
         <v>1</v>
@@ -4768,13 +4780,13 @@
         <v>2013</v>
       </c>
       <c r="C109" t="n">
-        <v>11.78338829960116</v>
+        <v>12.10863458373527</v>
       </c>
       <c r="D109" t="n">
-        <v>3.62550379680292</v>
+        <v>3.332964705444057</v>
       </c>
       <c r="E109" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F109" t="n">
         <v>15.49149116335467</v>
@@ -4786,13 +4798,13 @@
         <v>19</v>
       </c>
       <c r="I109" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J109" t="n">
-        <v>0.01163816627608508</v>
+        <v>0.0171540598403945</v>
       </c>
       <c r="K109" t="n">
-        <v>0.3491449882825525</v>
+        <v>0.5146217952118349</v>
       </c>
       <c r="L109" t="b">
         <v>0</v>
@@ -4808,13 +4820,13 @@
         <v>2014</v>
       </c>
       <c r="C110" t="n">
-        <v>12.06577895176723</v>
+        <v>11.93208529595366</v>
       </c>
       <c r="D110" t="n">
-        <v>2.929059640471634</v>
+        <v>2.93128528446317</v>
       </c>
       <c r="E110" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F110" t="n">
         <v>17.71606643090326</v>
@@ -4826,13 +4838,13 @@
         <v>19</v>
       </c>
       <c r="I110" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J110" t="n">
-        <v>1.236004823829212e-06</v>
+        <v>1.428791751851023e-06</v>
       </c>
       <c r="K110" t="n">
-        <v>3.708014471487635e-05</v>
+        <v>4.28637525555307e-05</v>
       </c>
       <c r="L110" t="b">
         <v>1</v>
@@ -4848,13 +4860,13 @@
         <v>2015</v>
       </c>
       <c r="C111" t="n">
-        <v>12.76803200984359</v>
+        <v>12.92092768098665</v>
       </c>
       <c r="D111" t="n">
-        <v>1.953411917738064</v>
+        <v>1.728896240135968</v>
       </c>
       <c r="E111" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F111" t="n">
         <v>15.47277052798838</v>
@@ -4869,10 +4881,10 @@
         <v>58</v>
       </c>
       <c r="J111" t="n">
-        <v>8.329215913250309e-05</v>
+        <v>0.0001340811834087878</v>
       </c>
       <c r="K111" t="n">
-        <v>0.002498764773975092</v>
+        <v>0.004022435502263635</v>
       </c>
       <c r="L111" t="b">
         <v>1</v>
@@ -4888,13 +4900,13 @@
         <v>2016</v>
       </c>
       <c r="C112" t="n">
-        <v>10.01404058174387</v>
+        <v>9.784465099813245</v>
       </c>
       <c r="D112" t="n">
-        <v>2.454048339494762</v>
+        <v>2.525240708408105</v>
       </c>
       <c r="E112" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F112" t="n">
         <v>19.40724972296806</v>
@@ -4909,10 +4921,10 @@
         <v>2</v>
       </c>
       <c r="J112" t="n">
-        <v>6.708507279434098e-08</v>
+        <v>9.526002607574446e-08</v>
       </c>
       <c r="K112" t="n">
-        <v>2.012552183830229e-06</v>
+        <v>2.857800782272334e-06</v>
       </c>
       <c r="L112" t="b">
         <v>1</v>
@@ -4928,13 +4940,13 @@
         <v>2017</v>
       </c>
       <c r="C113" t="n">
-        <v>9.122979554354034</v>
+        <v>8.734319237597978</v>
       </c>
       <c r="D113" t="n">
-        <v>2.932776203533434</v>
+        <v>2.980363654765043</v>
       </c>
       <c r="E113" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F113" t="n">
         <v>14.06259837992341</v>
@@ -4946,13 +4958,13 @@
         <v>19</v>
       </c>
       <c r="I113" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J113" t="n">
-        <v>3.059769375220792e-06</v>
+        <v>2.792418774425856e-06</v>
       </c>
       <c r="K113" t="n">
-        <v>9.179308125662376e-05</v>
+        <v>8.377256323277568e-05</v>
       </c>
       <c r="L113" t="b">
         <v>1</v>
@@ -4968,13 +4980,13 @@
         <v>2018</v>
       </c>
       <c r="C114" t="n">
-        <v>16.28268627051395</v>
+        <v>16.42611149845553</v>
       </c>
       <c r="D114" t="n">
-        <v>2.243859294352716</v>
+        <v>2.201086134017053</v>
       </c>
       <c r="E114" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F114" t="n">
         <v>19.84710624882389</v>
@@ -4989,10 +5001,10 @@
         <v>38</v>
       </c>
       <c r="J114" t="n">
-        <v>8.287791050984357e-06</v>
+        <v>1.297546732209478e-05</v>
       </c>
       <c r="K114" t="n">
-        <v>0.0002486337315295307</v>
+        <v>0.0003892640196628434</v>
       </c>
       <c r="L114" t="b">
         <v>1</v>
@@ -5008,13 +5020,13 @@
         <v>2019</v>
       </c>
       <c r="C115" t="n">
-        <v>12.2016970324664</v>
+        <v>12.21074259338828</v>
       </c>
       <c r="D115" t="n">
-        <v>3.077398351180634</v>
+        <v>3.153656278420741</v>
       </c>
       <c r="E115" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F115" t="n">
         <v>16.92833909300798</v>
@@ -5029,10 +5041,10 @@
         <v>49</v>
       </c>
       <c r="J115" t="n">
-        <v>3.045679503082353e-05</v>
+        <v>4.853023332476458e-05</v>
       </c>
       <c r="K115" t="n">
-        <v>0.000913703850924706</v>
+        <v>0.001455906999742938</v>
       </c>
       <c r="L115" t="b">
         <v>1</v>
@@ -5048,13 +5060,13 @@
         <v>2020</v>
       </c>
       <c r="C116" t="n">
-        <v>14.3441668257399</v>
+        <v>14.50768259463136</v>
       </c>
       <c r="D116" t="n">
-        <v>1.632403150083514</v>
+        <v>1.672859913727776</v>
       </c>
       <c r="E116" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F116" t="n">
         <v>19.69032546393504</v>
@@ -5069,10 +5081,10 @@
         <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>5.00601038421188e-08</v>
+        <v>7.057183580218095e-08</v>
       </c>
       <c r="K116" t="n">
-        <v>1.501803115263564e-06</v>
+        <v>2.117155074065429e-06</v>
       </c>
       <c r="L116" t="b">
         <v>1</v>
@@ -5088,13 +5100,13 @@
         <v>2021</v>
       </c>
       <c r="C117" t="n">
-        <v>9.122871792953639</v>
+        <v>9.466478714520807</v>
       </c>
       <c r="D117" t="n">
-        <v>3.194883058959056</v>
+        <v>3.127128947791165</v>
       </c>
       <c r="E117" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F117" t="n">
         <v>18.95609104268526</v>
@@ -5106,13 +5118,13 @@
         <v>19</v>
       </c>
       <c r="I117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J117" t="n">
-        <v>5.00601038421188e-08</v>
+        <v>9.526002607574446e-08</v>
       </c>
       <c r="K117" t="n">
-        <v>1.501803115263564e-06</v>
+        <v>2.857800782272334e-06</v>
       </c>
       <c r="L117" t="b">
         <v>1</v>
@@ -5128,13 +5140,13 @@
         <v>2022</v>
       </c>
       <c r="C118" t="n">
-        <v>11.30509767714965</v>
+        <v>11.45119120127827</v>
       </c>
       <c r="D118" t="n">
-        <v>2.629919074024675</v>
+        <v>2.529118102749644</v>
       </c>
       <c r="E118" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F118" t="n">
         <v>16.67880363595425</v>
@@ -5149,10 +5161,10 @@
         <v>74</v>
       </c>
       <c r="J118" t="n">
-        <v>0.0004374167278753596</v>
+        <v>0.0007104983619273451</v>
       </c>
       <c r="K118" t="n">
-        <v>0.01312250183626079</v>
+        <v>0.02131495085782036</v>
       </c>
       <c r="L118" t="b">
         <v>1</v>
@@ -5168,13 +5180,13 @@
         <v>2023</v>
       </c>
       <c r="C119" t="n">
-        <v>10.0158753214377</v>
+        <v>10.05132637114107</v>
       </c>
       <c r="D119" t="n">
-        <v>2.646840364312413</v>
+        <v>2.476073987536192</v>
       </c>
       <c r="E119" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F119" t="n">
         <v>21.3847286490564</v>
@@ -5189,10 +5201,10 @@
         <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>5.00601038421188e-08</v>
+        <v>7.057183580218095e-08</v>
       </c>
       <c r="K119" t="n">
-        <v>1.501803115263564e-06</v>
+        <v>2.117155074065429e-06</v>
       </c>
       <c r="L119" t="b">
         <v>1</v>
@@ -5208,13 +5220,13 @@
         <v>2024</v>
       </c>
       <c r="C120" t="n">
-        <v>11.58393603308826</v>
+        <v>11.06972276013619</v>
       </c>
       <c r="D120" t="n">
-        <v>4.895179877286342</v>
+        <v>4.523514021448938</v>
       </c>
       <c r="E120" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F120" t="n">
         <v>17.1364466173294</v>
@@ -5226,13 +5238,13 @@
         <v>19</v>
       </c>
       <c r="I120" t="n">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="J120" t="n">
-        <v>0.005363128648524343</v>
+        <v>0.001841595484321759</v>
       </c>
       <c r="K120" t="n">
-        <v>0.1608938594557303</v>
+        <v>0.05524786452965277</v>
       </c>
       <c r="L120" t="b">
         <v>0</v>
@@ -5248,13 +5260,13 @@
         <v>2025</v>
       </c>
       <c r="C121" t="n">
-        <v>14.22282140231187</v>
+        <v>14.35379052313565</v>
       </c>
       <c r="D121" t="n">
-        <v>2.452342800770946</v>
+        <v>2.163819483831811</v>
       </c>
       <c r="E121" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F121" t="n">
         <v>17.80238783760911</v>
@@ -5266,13 +5278,13 @@
         <v>19</v>
       </c>
       <c r="I121" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="J121" t="n">
-        <v>3.045679503082353e-05</v>
+        <v>2.692652717951664e-05</v>
       </c>
       <c r="K121" t="n">
-        <v>0.000913703850924706</v>
+        <v>0.0008077958153854991</v>
       </c>
       <c r="L121" t="b">
         <v>1</v>
